--- a/ozone/multistate/MAE_stacked_VTZP_MS_3_70_30.xlsx
+++ b/ozone/multistate/MAE_stacked_VTZP_MS_3_70_30.xlsx
@@ -447,10 +447,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1326555203760932</v>
+        <v>0.1293155931684369</v>
       </c>
       <c r="C2" t="n">
-        <v>1.887766762152276</v>
+        <v>1.607584710519916</v>
       </c>
     </row>
     <row r="3">
@@ -460,10 +460,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1540962491509259</v>
+        <v>0.1525824567035311</v>
       </c>
       <c r="C3" t="n">
-        <v>2.7740479412422</v>
+        <v>2.512406748685692</v>
       </c>
     </row>
   </sheetData>
